--- a/Result/profitability/5211.xlsx
+++ b/Result/profitability/5211.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1137500000000001</v>
+        <v>-0.07250000000000008</v>
       </c>
       <c r="N2" t="n">
-        <v>51.97125</v>
+        <v>50.49375000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007499999999999923</v>
+        <v>0.02999999999999993</v>
       </c>
       <c r="N3" t="n">
-        <v>53.39874999999999</v>
+        <v>52.28625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1087499999999999</v>
+        <v>0.135</v>
       </c>
       <c r="N4" t="n">
-        <v>55.06375000000001</v>
+        <v>54.2825</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2049999999999999</v>
+        <v>0.2349999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>56.92</v>
+        <v>55.7025</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0.32</v>
+        <v>0.3224999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>58.54375</v>
+        <v>58.39875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4024999999999999</v>
+        <v>0.4062499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>61.47625</v>
+        <v>61.46375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4787499999999999</v>
+        <v>0.4924999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>63.91</v>
+        <v>64.075</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.63</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.58</v>
       </c>
       <c r="N9" t="n">
         <v>67.23625</v>
@@ -1645,7 +1645,7 @@
         <v>0.97</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6137499999999999</v>
+        <v>0.61375</v>
       </c>
       <c r="N10" t="n">
         <v>67.87375</v>
@@ -1899,7 +1899,7 @@
         <v>0.73</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6924999999999999</v>
+        <v>0.6925</v>
       </c>
       <c r="N12" t="n">
         <v>67.87375</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>71</v>
+      </c>
+      <c r="D75" t="n">
+        <v>39</v>
+      </c>
+      <c r="E75" t="n">
+        <v>32</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2100000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>49.12125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.611111111111111</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03054141601110594</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7741935483870968</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.740000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.179439941046426</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
